--- a/fixtures/dirty.xlsx
+++ b/fixtures/dirty.xlsx
@@ -10,6 +10,14 @@
     <definedName name="margin">#REF!</definedName>
   </definedNames>
 </workbook>
+</file>
+
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="RatesTemplate" type="4" refreshedVersion="0" background="1">
+    <webPr xml="1" sourceData="1" url="N:\_Templates\rates\RatesTemplate.xml" htmlTables="1"/>
+  </connection>
+</connections>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
